--- a/docs/FRENCH-REVIEW.xlsx
+++ b/docs/FRENCH-REVIEW.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -556,6 +556,18 @@
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Сообщения НСтр просмотрены выборочно: 10 тысяч строк за один проход глазами не разобрать. Второй проход — по модулям, начиная с печатных форм и сообщений пользователю.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Лист «Правки» внесён в исходники 2026-09-07 (версия 2.0.14.12) вместе с терминами из базы Ахмеда: Entrepôt/Warehouse/Almacén, Montant/Amount/Importe, Quantité, Articles/Items/Artículos, Payé, Commande client. Листы «Не переведено» и «Типографика» (кроме мусорных апострофов) — не внесены.</t>
         </is>
       </c>
     </row>
